--- a/ResourcesBD/section_bulk_file.xlsx
+++ b/ResourcesBD/section_bulk_file.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation\ExcelGenerator\ResourcesBD\"/>
     </mc:Choice>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="83">
   <si>
     <t>Distributor Code</t>
   </si>
@@ -88,12 +88,193 @@
   </si>
   <si>
     <t>Test</t>
+  </si>
+  <si>
+    <t>AUTOSEC61B8</t>
+  </si>
+  <si>
+    <t>AUTOSEC4FEE</t>
+  </si>
+  <si>
+    <t>AUTOSECC8F5</t>
+  </si>
+  <si>
+    <t>AUTOSEC39AB</t>
+  </si>
+  <si>
+    <t>AUTOSEC44BE</t>
+  </si>
+  <si>
+    <t>AUTOSECCD99</t>
+  </si>
+  <si>
+    <t>AUTOSEC40EC</t>
+  </si>
+  <si>
+    <t>AUTOSEC0B74</t>
+  </si>
+  <si>
+    <t>AUTOSEC4B51</t>
+  </si>
+  <si>
+    <t>AUTOSEC872C</t>
+  </si>
+  <si>
+    <t>AUTOSECD6F9</t>
+  </si>
+  <si>
+    <t>AUTOSEC7216</t>
+  </si>
+  <si>
+    <t>AUTOSEC6C99</t>
+  </si>
+  <si>
+    <t>AUTOSECA157</t>
+  </si>
+  <si>
+    <t>AUTOSEC4369</t>
+  </si>
+  <si>
+    <t>AUTOSECDCF7</t>
+  </si>
+  <si>
+    <t>AUTOSEC2FF7</t>
+  </si>
+  <si>
+    <t>AUTOSEC51B0</t>
+  </si>
+  <si>
+    <t>AUTOSECBCDF</t>
+  </si>
+  <si>
+    <t>AUTOSEC5C2F</t>
+  </si>
+  <si>
+    <t>AUTOSEC6302</t>
+  </si>
+  <si>
+    <t>AUTOSECC660</t>
+  </si>
+  <si>
+    <t>AUTOSECB51D</t>
+  </si>
+  <si>
+    <t>AUTOSEC9F6D</t>
+  </si>
+  <si>
+    <t>AUTOSEC593A</t>
+  </si>
+  <si>
+    <t>AUTOSEC6FC4</t>
+  </si>
+  <si>
+    <t>AUTOSECCE07</t>
+  </si>
+  <si>
+    <t>AUTOSEC8693</t>
+  </si>
+  <si>
+    <t>AUTOSEC47DC</t>
+  </si>
+  <si>
+    <t>AUTOSECEB6C</t>
+  </si>
+  <si>
+    <t>AUTOSEC1127</t>
+  </si>
+  <si>
+    <t>AUTOSEC1229</t>
+  </si>
+  <si>
+    <t>AUTOSEC3C61</t>
+  </si>
+  <si>
+    <t>AUTOSECA498</t>
+  </si>
+  <si>
+    <t>AUTOSEC0EC6</t>
+  </si>
+  <si>
+    <t>AUTOSECFB42</t>
+  </si>
+  <si>
+    <t>AUTOSEC0173</t>
+  </si>
+  <si>
+    <t>AUTOSEC98E8</t>
+  </si>
+  <si>
+    <t>AUTOSECEC8D</t>
+  </si>
+  <si>
+    <t>AUTOSEC933A</t>
+  </si>
+  <si>
+    <t>AUTOSEC4F8A</t>
+  </si>
+  <si>
+    <t>AUTOSEC720A</t>
+  </si>
+  <si>
+    <t>AUTOSECF6FE</t>
+  </si>
+  <si>
+    <t>AUTOSECBE6A</t>
+  </si>
+  <si>
+    <t>AUTOSECA5BB</t>
+  </si>
+  <si>
+    <t>AUTOSEC0337</t>
+  </si>
+  <si>
+    <t>AUTOSEC3D54</t>
+  </si>
+  <si>
+    <t>AUTOSEC3560</t>
+  </si>
+  <si>
+    <t>AUTOSEC87E6</t>
+  </si>
+  <si>
+    <t>AUTOSEC8758</t>
+  </si>
+  <si>
+    <t>AUTOSEC53D5</t>
+  </si>
+  <si>
+    <t>AUTOSECB12A</t>
+  </si>
+  <si>
+    <t>AUTOSECFF06</t>
+  </si>
+  <si>
+    <t>AUTOSECEC6D</t>
+  </si>
+  <si>
+    <t>AUTOSECF177</t>
+  </si>
+  <si>
+    <t>AUTOSEC06F6</t>
+  </si>
+  <si>
+    <t>AUTOSEC9F72</t>
+  </si>
+  <si>
+    <t>AUTOSEC5477</t>
+  </si>
+  <si>
+    <t>AUTOSEC43DC</t>
+  </si>
+  <si>
+    <t>AUTOSECF183</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -408,122 +589,122 @@
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="19.7265625" customWidth="1"/>
+    <col min="4" max="4" customWidth="true" width="19.7265625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" t="s" s="0">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>21</v>
       </c>
     </row>

--- a/ResourcesBD/section_bulk_file.xlsx
+++ b/ResourcesBD/section_bulk_file.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="122">
   <si>
     <t>Distributor Code</t>
   </si>
@@ -268,6 +268,123 @@
   </si>
   <si>
     <t>AUTOSECF183</t>
+  </si>
+  <si>
+    <t>AUTOSEC1456</t>
+  </si>
+  <si>
+    <t>AUTOSEC123B</t>
+  </si>
+  <si>
+    <t>AUTOSEC2DCE</t>
+  </si>
+  <si>
+    <t>AUTOSECE05F</t>
+  </si>
+  <si>
+    <t>AUTOSECAC88</t>
+  </si>
+  <si>
+    <t>AUTOSEC5F72</t>
+  </si>
+  <si>
+    <t>AUTOSEC0ECB</t>
+  </si>
+  <si>
+    <t>AUTOSEC47CE</t>
+  </si>
+  <si>
+    <t>AUTOSEC740C</t>
+  </si>
+  <si>
+    <t>AUTOSECC3AE</t>
+  </si>
+  <si>
+    <t>AUTOSECFEE2</t>
+  </si>
+  <si>
+    <t>AUTOSECB750</t>
+  </si>
+  <si>
+    <t>AUTOSECB370</t>
+  </si>
+  <si>
+    <t>AUTOSEC0582</t>
+  </si>
+  <si>
+    <t>AUTOSECAFEB</t>
+  </si>
+  <si>
+    <t>AUTOSEC0384</t>
+  </si>
+  <si>
+    <t>AUTOSEC5D8D</t>
+  </si>
+  <si>
+    <t>AUTOSECD372</t>
+  </si>
+  <si>
+    <t>AUTOSEC22F6</t>
+  </si>
+  <si>
+    <t>AUTOSEC395A</t>
+  </si>
+  <si>
+    <t>AUTOSECBBD8</t>
+  </si>
+  <si>
+    <t>AUTOSECEEA3</t>
+  </si>
+  <si>
+    <t>AUTOSEC2D3F</t>
+  </si>
+  <si>
+    <t>AUTOSEC7DE7</t>
+  </si>
+  <si>
+    <t>AUTOSEC3040</t>
+  </si>
+  <si>
+    <t>AUTOSEC2E2B</t>
+  </si>
+  <si>
+    <t>AUTOSECF7D2</t>
+  </si>
+  <si>
+    <t>AUTOSEC5C5E</t>
+  </si>
+  <si>
+    <t>AUTOSEC3EC9</t>
+  </si>
+  <si>
+    <t>AUTOSEC534F</t>
+  </si>
+  <si>
+    <t>AUTOSEC183A</t>
+  </si>
+  <si>
+    <t>AUTOSECF7CF</t>
+  </si>
+  <si>
+    <t>AUTOSECA027</t>
+  </si>
+  <si>
+    <t>AUTOSECED77</t>
+  </si>
+  <si>
+    <t>AUTOSECB896</t>
+  </si>
+  <si>
+    <t>AUTOSEC3A3A</t>
+  </si>
+  <si>
+    <t>AUTOSECBE90</t>
+  </si>
+  <si>
+    <t>AUTOSEC1236</t>
+  </si>
+  <si>
+    <t>AUTOSEC1E33</t>
   </si>
 </sst>
 </file>
@@ -626,7 +743,7 @@
         <v>9</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>11</v>
@@ -655,7 +772,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>11</v>
@@ -684,7 +801,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>11</v>
